--- a/output/yearly_population_iteration_22_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_22_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6586</v>
+        <v>4314</v>
       </c>
       <c r="C2" t="n">
-        <v>8662</v>
+        <v>7987</v>
       </c>
       <c r="D2" t="n">
-        <v>38401</v>
+        <v>31206</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3704</v>
+        <v>3071</v>
       </c>
       <c r="C3" t="n">
-        <v>3630</v>
+        <v>4772</v>
       </c>
       <c r="D3" t="n">
-        <v>19575</v>
+        <v>14491</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2799</v>
+        <v>2435</v>
       </c>
       <c r="C4" t="n">
-        <v>3434</v>
+        <v>4661</v>
       </c>
       <c r="D4" t="n">
-        <v>8025</v>
+        <v>7926</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1807</v>
+        <v>1692</v>
       </c>
       <c r="C5" t="n">
-        <v>2896</v>
+        <v>4489</v>
       </c>
       <c r="D5" t="n">
-        <v>2704</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>980</v>
+        <v>942</v>
       </c>
       <c r="C6" t="n">
-        <v>2036</v>
+        <v>3648</v>
       </c>
       <c r="D6" t="n">
-        <v>1105</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>467</v>
+        <v>422</v>
       </c>
       <c r="C7" t="n">
-        <v>1164</v>
+        <v>2282</v>
       </c>
       <c r="D7" t="n">
-        <v>649</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="C8" t="n">
-        <v>611</v>
+        <v>1050</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>315</v>
+        <v>411</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7226</v>
+        <v>6044</v>
       </c>
       <c r="C2" t="n">
-        <v>6610</v>
+        <v>10529</v>
       </c>
       <c r="D2" t="n">
-        <v>32754</v>
+        <v>23476</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4085</v>
+        <v>2984</v>
       </c>
       <c r="C3" t="n">
-        <v>5276</v>
+        <v>5467</v>
       </c>
       <c r="D3" t="n">
-        <v>20939</v>
+        <v>15929</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2771</v>
+        <v>2312</v>
       </c>
       <c r="C4" t="n">
-        <v>3427</v>
+        <v>4616</v>
       </c>
       <c r="D4" t="n">
-        <v>9776</v>
+        <v>8617</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1986</v>
+        <v>1778</v>
       </c>
       <c r="C5" t="n">
-        <v>3099</v>
+        <v>4430</v>
       </c>
       <c r="D5" t="n">
-        <v>3464</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1236</v>
+        <v>1142</v>
       </c>
       <c r="C6" t="n">
-        <v>2399</v>
+        <v>3984</v>
       </c>
       <c r="D6" t="n">
-        <v>1350</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>620</v>
+        <v>575</v>
       </c>
       <c r="C7" t="n">
-        <v>1573</v>
+        <v>2847</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>774</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="C8" t="n">
-        <v>860</v>
+        <v>1568</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C9" t="n">
-        <v>439</v>
+        <v>663</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>254</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9517</v>
+        <v>8246</v>
       </c>
       <c r="C2" t="n">
-        <v>6856</v>
+        <v>8214</v>
       </c>
       <c r="D2" t="n">
-        <v>36998</v>
+        <v>25072</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4400</v>
+        <v>3390</v>
       </c>
       <c r="C3" t="n">
-        <v>5172</v>
+        <v>6645</v>
       </c>
       <c r="D3" t="n">
-        <v>21077</v>
+        <v>15815</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2832</v>
+        <v>2201</v>
       </c>
       <c r="C4" t="n">
-        <v>4174</v>
+        <v>4835</v>
       </c>
       <c r="D4" t="n">
-        <v>11099</v>
+        <v>9325</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2058</v>
+        <v>1777</v>
       </c>
       <c r="C5" t="n">
-        <v>3182</v>
+        <v>4372</v>
       </c>
       <c r="D5" t="n">
-        <v>4328</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1428</v>
+        <v>1281</v>
       </c>
       <c r="C6" t="n">
-        <v>2655</v>
+        <v>4128</v>
       </c>
       <c r="D6" t="n">
-        <v>1623</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>783</v>
+        <v>709</v>
       </c>
       <c r="C7" t="n">
-        <v>1928</v>
+        <v>3263</v>
       </c>
       <c r="D7" t="n">
-        <v>794</v>
+        <v>879</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>363</v>
+        <v>317</v>
       </c>
       <c r="C8" t="n">
-        <v>1144</v>
+        <v>2040</v>
       </c>
       <c r="D8" t="n">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="C9" t="n">
-        <v>607</v>
+        <v>999</v>
       </c>
       <c r="D9" t="n">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>322</v>
+        <v>421</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8486</v>
+        <v>7354</v>
       </c>
       <c r="C2" t="n">
-        <v>4497</v>
+        <v>5651</v>
       </c>
       <c r="D2" t="n">
-        <v>30111</v>
+        <v>20816</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5299</v>
+        <v>4012</v>
       </c>
       <c r="C3" t="n">
-        <v>7555</v>
+        <v>9295</v>
       </c>
       <c r="D3" t="n">
-        <v>23023</v>
+        <v>17287</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1901</v>
+        <v>1641</v>
       </c>
       <c r="C4" t="n">
-        <v>5458</v>
+        <v>6842</v>
       </c>
       <c r="D4" t="n">
-        <v>10301</v>
+        <v>9186</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1319</v>
+        <v>1183</v>
       </c>
       <c r="C5" t="n">
-        <v>2601</v>
+        <v>4045</v>
       </c>
       <c r="D5" t="n">
-        <v>2795</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>723</v>
+        <v>655</v>
       </c>
       <c r="C6" t="n">
-        <v>1889</v>
+        <v>3197</v>
       </c>
       <c r="D6" t="n">
-        <v>778</v>
+        <v>861</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>335</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>1121</v>
+        <v>1999</v>
       </c>
       <c r="D7" t="n">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>594</v>
+        <v>979</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>315</v>
+        <v>412</v>
       </c>
       <c r="D9" t="n">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5070</v>
+        <v>4374</v>
       </c>
       <c r="C2" t="n">
-        <v>1976</v>
+        <v>3238</v>
       </c>
       <c r="D2" t="n">
-        <v>20778</v>
+        <v>14840</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5740</v>
+        <v>4609</v>
       </c>
       <c r="C3" t="n">
-        <v>5533</v>
+        <v>6945</v>
       </c>
       <c r="D3" t="n">
-        <v>22901</v>
+        <v>16937</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2807</v>
+        <v>2224</v>
       </c>
       <c r="C4" t="n">
-        <v>6508</v>
+        <v>8092</v>
       </c>
       <c r="D4" t="n">
-        <v>12040</v>
+        <v>10161</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1473</v>
+        <v>1286</v>
       </c>
       <c r="C5" t="n">
-        <v>3905</v>
+        <v>5282</v>
       </c>
       <c r="D5" t="n">
-        <v>3799</v>
+        <v>3778</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>881</v>
+        <v>779</v>
       </c>
       <c r="C6" t="n">
-        <v>2263</v>
+        <v>3646</v>
       </c>
       <c r="D6" t="n">
-        <v>985</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="C7" t="n">
-        <v>1426</v>
+        <v>2491</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>780</v>
+        <v>1276</v>
       </c>
       <c r="D8" t="n">
-        <v>344</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>372</v>
+        <v>460</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5827</v>
+        <v>4027</v>
       </c>
       <c r="C2" t="n">
-        <v>5979</v>
+        <v>6448</v>
       </c>
       <c r="D2" t="n">
-        <v>17422</v>
+        <v>15567</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4572</v>
+        <v>3786</v>
       </c>
       <c r="C3" t="n">
-        <v>3350</v>
+        <v>4588</v>
       </c>
       <c r="D3" t="n">
-        <v>21019</v>
+        <v>15513</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3537</v>
+        <v>2784</v>
       </c>
       <c r="C4" t="n">
-        <v>5876</v>
+        <v>7439</v>
       </c>
       <c r="D4" t="n">
-        <v>13550</v>
+        <v>10957</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1814</v>
+        <v>1492</v>
       </c>
       <c r="C5" t="n">
-        <v>5098</v>
+        <v>6466</v>
       </c>
       <c r="D5" t="n">
-        <v>5028</v>
+        <v>4643</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1040</v>
+        <v>905</v>
       </c>
       <c r="C6" t="n">
-        <v>3034</v>
+        <v>4333</v>
       </c>
       <c r="D6" t="n">
-        <v>1404</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>482</v>
+        <v>411</v>
       </c>
       <c r="C7" t="n">
-        <v>1816</v>
+        <v>3012</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="C8" t="n">
-        <v>1059</v>
+        <v>1776</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>535</v>
+        <v>768</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>102</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3366</v>
+        <v>2379</v>
       </c>
       <c r="C2" t="n">
-        <v>2657</v>
+        <v>3018</v>
       </c>
       <c r="D2" t="n">
-        <v>12094</v>
+        <v>10866</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4717</v>
+        <v>3740</v>
       </c>
       <c r="C3" t="n">
-        <v>4178</v>
+        <v>5073</v>
       </c>
       <c r="D3" t="n">
-        <v>20111</v>
+        <v>15171</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3938</v>
+        <v>3067</v>
       </c>
       <c r="C4" t="n">
-        <v>5477</v>
+        <v>7067</v>
       </c>
       <c r="D4" t="n">
-        <v>14505</v>
+        <v>11588</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1893</v>
+        <v>1571</v>
       </c>
       <c r="C5" t="n">
-        <v>5945</v>
+        <v>7722</v>
       </c>
       <c r="D5" t="n">
-        <v>5484</v>
+        <v>4885</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>887</v>
+        <v>747</v>
       </c>
       <c r="C6" t="n">
-        <v>3809</v>
+        <v>5276</v>
       </c>
       <c r="D6" t="n">
-        <v>1375</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>1941</v>
+        <v>3178</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>866</v>
+        <v>1292</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4188</v>
+        <v>2553</v>
       </c>
       <c r="C2" t="n">
-        <v>5998</v>
+        <v>7921</v>
       </c>
       <c r="D2" t="n">
-        <v>12161</v>
+        <v>10213</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3529</v>
+        <v>2724</v>
       </c>
       <c r="C3" t="n">
-        <v>3070</v>
+        <v>3690</v>
       </c>
       <c r="D3" t="n">
-        <v>17765</v>
+        <v>13711</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3761</v>
+        <v>2915</v>
       </c>
       <c r="C4" t="n">
-        <v>4727</v>
+        <v>5982</v>
       </c>
       <c r="D4" t="n">
-        <v>14978</v>
+        <v>11786</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2413</v>
+        <v>1927</v>
       </c>
       <c r="C5" t="n">
-        <v>5658</v>
+        <v>7339</v>
       </c>
       <c r="D5" t="n">
-        <v>6702</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1159</v>
+        <v>968</v>
       </c>
       <c r="C6" t="n">
-        <v>4790</v>
+        <v>6364</v>
       </c>
       <c r="D6" t="n">
-        <v>1962</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>346</v>
+        <v>278</v>
       </c>
       <c r="C7" t="n">
-        <v>2728</v>
+        <v>4030</v>
       </c>
       <c r="D7" t="n">
-        <v>681</v>
+        <v>697</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>1293</v>
+        <v>2000</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>487</v>
+        <v>633</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>44</v>
+      </c>
+      <c r="D14" t="n">
         <v>47</v>
-      </c>
-      <c r="D14" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2905</v>
+        <v>1790</v>
       </c>
       <c r="C2" t="n">
-        <v>3716</v>
+        <v>4909</v>
       </c>
       <c r="D2" t="n">
-        <v>9425</v>
+        <v>8360</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3284</v>
+        <v>2339</v>
       </c>
       <c r="C3" t="n">
-        <v>3876</v>
+        <v>4906</v>
       </c>
       <c r="D3" t="n">
-        <v>16223</v>
+        <v>12545</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3397</v>
+        <v>2633</v>
       </c>
       <c r="C4" t="n">
-        <v>4048</v>
+        <v>5105</v>
       </c>
       <c r="D4" t="n">
-        <v>15041</v>
+        <v>11912</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2664</v>
+        <v>2095</v>
       </c>
       <c r="C5" t="n">
-        <v>5400</v>
+        <v>6915</v>
       </c>
       <c r="D5" t="n">
-        <v>7515</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1403</v>
+        <v>1146</v>
       </c>
       <c r="C6" t="n">
-        <v>5273</v>
+        <v>6932</v>
       </c>
       <c r="D6" t="n">
-        <v>2450</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>251</v>
       </c>
       <c r="C7" t="n">
-        <v>3459</v>
+        <v>4876</v>
       </c>
       <c r="D7" t="n">
-        <v>777</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1673</v>
+        <v>2524</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>594</v>
+        <v>735</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4373</v>
+        <v>2651</v>
       </c>
       <c r="C2" t="n">
-        <v>6246</v>
+        <v>7582</v>
       </c>
       <c r="D2" t="n">
-        <v>11886</v>
+        <v>11269</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2641</v>
+        <v>1805</v>
       </c>
       <c r="C3" t="n">
-        <v>3406</v>
+        <v>4404</v>
       </c>
       <c r="D3" t="n">
-        <v>14288</v>
+        <v>11239</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2944</v>
+        <v>2198</v>
       </c>
       <c r="C4" t="n">
-        <v>3848</v>
+        <v>4914</v>
       </c>
       <c r="D4" t="n">
-        <v>14765</v>
+        <v>11641</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2662</v>
+        <v>2098</v>
       </c>
       <c r="C5" t="n">
-        <v>4755</v>
+        <v>6041</v>
       </c>
       <c r="D5" t="n">
-        <v>8370</v>
+        <v>6799</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1719</v>
+        <v>1362</v>
       </c>
       <c r="C6" t="n">
-        <v>5277</v>
+        <v>6867</v>
       </c>
       <c r="D6" t="n">
-        <v>3098</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>617</v>
+        <v>470</v>
       </c>
       <c r="C7" t="n">
-        <v>4168</v>
+        <v>5639</v>
       </c>
       <c r="D7" t="n">
-        <v>982</v>
+        <v>933</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>2353</v>
+        <v>3377</v>
       </c>
       <c r="D8" t="n">
-        <v>469</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>969</v>
+        <v>1320</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>65</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5119</v>
+        <v>5062</v>
       </c>
       <c r="C2" t="n">
-        <v>4111</v>
+        <v>9395</v>
       </c>
       <c r="D2" t="n">
-        <v>6454</v>
+        <v>19970</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3062</v>
+        <v>1897</v>
       </c>
       <c r="C2" t="n">
-        <v>3447</v>
+        <v>4306</v>
       </c>
       <c r="D2" t="n">
-        <v>8748</v>
+        <v>8293</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3607</v>
+        <v>2482</v>
       </c>
       <c r="C3" t="n">
-        <v>4393</v>
+        <v>5521</v>
       </c>
       <c r="D3" t="n">
-        <v>15327</v>
+        <v>12292</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3942</v>
+        <v>3041</v>
       </c>
       <c r="C4" t="n">
-        <v>5488</v>
+        <v>7038</v>
       </c>
       <c r="D4" t="n">
-        <v>15252</v>
+        <v>12024</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1711</v>
+        <v>1316</v>
       </c>
       <c r="C5" t="n">
-        <v>7229</v>
+        <v>9327</v>
       </c>
       <c r="D5" t="n">
-        <v>7594</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>570</v>
+        <v>434</v>
       </c>
       <c r="C6" t="n">
-        <v>5222</v>
+        <v>6872</v>
       </c>
       <c r="D6" t="n">
-        <v>2376</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>2305</v>
+        <v>3309</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>949</v>
+        <v>1293</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>63</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6084</v>
+        <v>5948</v>
       </c>
       <c r="C2" t="n">
-        <v>4239</v>
+        <v>7219</v>
       </c>
       <c r="D2" t="n">
-        <v>13174</v>
+        <v>21880</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2176</v>
+        <v>2151</v>
       </c>
       <c r="C3" t="n">
-        <v>2104</v>
+        <v>4735</v>
       </c>
       <c r="D3" t="n">
-        <v>1775</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3976</v>
+        <v>4588</v>
       </c>
       <c r="C2" t="n">
-        <v>2629</v>
+        <v>10568</v>
       </c>
       <c r="D2" t="n">
-        <v>17708</v>
+        <v>28857</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3390</v>
+        <v>3324</v>
       </c>
       <c r="C3" t="n">
-        <v>2870</v>
+        <v>5295</v>
       </c>
       <c r="D3" t="n">
-        <v>3559</v>
+        <v>6704</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="C4" t="n">
-        <v>1296</v>
+        <v>2818</v>
       </c>
       <c r="D4" t="n">
-        <v>1539</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4894</v>
+        <v>5793</v>
       </c>
       <c r="C2" t="n">
-        <v>4514</v>
+        <v>6699</v>
       </c>
       <c r="D2" t="n">
-        <v>24979</v>
+        <v>28919</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3034</v>
+        <v>3234</v>
       </c>
       <c r="C3" t="n">
-        <v>2364</v>
+        <v>7038</v>
       </c>
       <c r="D3" t="n">
-        <v>5566</v>
+        <v>9765</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1877</v>
+        <v>1796</v>
       </c>
       <c r="C4" t="n">
-        <v>2175</v>
+        <v>4138</v>
       </c>
       <c r="D4" t="n">
-        <v>1865</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="C5" t="n">
-        <v>814</v>
+        <v>1612</v>
       </c>
       <c r="D5" t="n">
-        <v>1217</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D9" t="n">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5882</v>
+        <v>5502</v>
       </c>
       <c r="C2" t="n">
-        <v>6697</v>
+        <v>5893</v>
       </c>
       <c r="D2" t="n">
-        <v>27388</v>
+        <v>24149</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3223</v>
+        <v>3619</v>
       </c>
       <c r="C3" t="n">
-        <v>3034</v>
+        <v>5987</v>
       </c>
       <c r="D3" t="n">
-        <v>8124</v>
+        <v>11988</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2104</v>
+        <v>2124</v>
       </c>
       <c r="C4" t="n">
-        <v>2233</v>
+        <v>5583</v>
       </c>
       <c r="D4" t="n">
-        <v>2465</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>969</v>
+        <v>910</v>
       </c>
       <c r="C5" t="n">
-        <v>1507</v>
+        <v>2848</v>
       </c>
       <c r="D5" t="n">
-        <v>1298</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C6" t="n">
-        <v>564</v>
+        <v>954</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6351</v>
+        <v>5453</v>
       </c>
       <c r="C2" t="n">
-        <v>3764</v>
+        <v>7168</v>
       </c>
       <c r="D2" t="n">
-        <v>39083</v>
+        <v>20273</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3298</v>
+        <v>3278</v>
       </c>
       <c r="C3" t="n">
-        <v>4045</v>
+        <v>4869</v>
       </c>
       <c r="D3" t="n">
-        <v>9859</v>
+        <v>12224</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1652</v>
+        <v>1755</v>
       </c>
       <c r="C4" t="n">
-        <v>2183</v>
+        <v>4746</v>
       </c>
       <c r="D4" t="n">
-        <v>2967</v>
+        <v>4661</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>814</v>
+        <v>786</v>
       </c>
       <c r="C5" t="n">
-        <v>1387</v>
+        <v>3076</v>
       </c>
       <c r="D5" t="n">
-        <v>1193</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>703</v>
+        <v>1272</v>
       </c>
       <c r="D6" t="n">
-        <v>755</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>295</v>
+        <v>408</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5986,7 +5986,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -5997,10 +5997,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5388</v>
+        <v>4364</v>
       </c>
       <c r="C2" t="n">
-        <v>5076</v>
+        <v>5228</v>
       </c>
       <c r="D2" t="n">
-        <v>40180</v>
+        <v>23052</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4036</v>
+        <v>3609</v>
       </c>
       <c r="C3" t="n">
-        <v>3316</v>
+        <v>5331</v>
       </c>
       <c r="D3" t="n">
-        <v>14261</v>
+        <v>12676</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2192</v>
+        <v>2199</v>
       </c>
       <c r="C4" t="n">
-        <v>3299</v>
+        <v>4720</v>
       </c>
       <c r="D4" t="n">
-        <v>4332</v>
+        <v>6044</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="C5" t="n">
-        <v>1839</v>
+        <v>3973</v>
       </c>
       <c r="D5" t="n">
-        <v>1502</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>522</v>
+        <v>481</v>
       </c>
       <c r="C6" t="n">
-        <v>1094</v>
+        <v>2248</v>
       </c>
       <c r="D6" t="n">
-        <v>832</v>
+        <v>921</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>530</v>
+        <v>890</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
         <v>284</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5189</v>
+        <v>4287</v>
       </c>
       <c r="C2" t="n">
-        <v>4595</v>
+        <v>6387</v>
       </c>
       <c r="D2" t="n">
-        <v>38927</v>
+        <v>26587</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3883</v>
+        <v>3274</v>
       </c>
       <c r="C3" t="n">
-        <v>3718</v>
+        <v>4575</v>
       </c>
       <c r="D3" t="n">
-        <v>17565</v>
+        <v>13545</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2706</v>
+        <v>2487</v>
       </c>
       <c r="C4" t="n">
-        <v>3240</v>
+        <v>4962</v>
       </c>
       <c r="D4" t="n">
-        <v>6201</v>
+        <v>7011</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1443</v>
+        <v>1433</v>
       </c>
       <c r="C5" t="n">
-        <v>2627</v>
+        <v>4291</v>
       </c>
       <c r="D5" t="n">
-        <v>1999</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>748</v>
+        <v>721</v>
       </c>
       <c r="C6" t="n">
-        <v>1488</v>
+        <v>3117</v>
       </c>
       <c r="D6" t="n">
-        <v>934</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>313</v>
+        <v>277</v>
       </c>
       <c r="C7" t="n">
-        <v>828</v>
+        <v>1572</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>404</v>
+        <v>605</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_22_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_22_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4314</v>
+        <v>7688</v>
       </c>
       <c r="C2" t="n">
-        <v>7987</v>
+        <v>7823</v>
       </c>
       <c r="D2" t="n">
-        <v>31206</v>
+        <v>21162</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3071</v>
+        <v>4397</v>
       </c>
       <c r="C3" t="n">
-        <v>4772</v>
+        <v>6715</v>
       </c>
       <c r="D3" t="n">
-        <v>14491</v>
+        <v>12061</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2435</v>
+        <v>3406</v>
       </c>
       <c r="C4" t="n">
-        <v>4661</v>
+        <v>5822</v>
       </c>
       <c r="D4" t="n">
-        <v>7926</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1692</v>
+        <v>2129</v>
       </c>
       <c r="C5" t="n">
-        <v>4489</v>
+        <v>4718</v>
       </c>
       <c r="D5" t="n">
-        <v>3324</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>942</v>
+        <v>1168</v>
       </c>
       <c r="C6" t="n">
-        <v>3648</v>
+        <v>3204</v>
       </c>
       <c r="D6" t="n">
-        <v>1350</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>422</v>
+        <v>544</v>
       </c>
       <c r="C7" t="n">
-        <v>2282</v>
+        <v>1796</v>
       </c>
       <c r="D7" t="n">
-        <v>684</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>157</v>
+        <v>209</v>
       </c>
       <c r="C8" t="n">
-        <v>1050</v>
+        <v>731</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6044</v>
+        <v>8590</v>
       </c>
       <c r="C2" t="n">
-        <v>10529</v>
+        <v>11030</v>
       </c>
       <c r="D2" t="n">
-        <v>23476</v>
+        <v>29025</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2984</v>
+        <v>4755</v>
       </c>
       <c r="C3" t="n">
-        <v>5467</v>
+        <v>6352</v>
       </c>
       <c r="D3" t="n">
-        <v>15929</v>
+        <v>12488</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2312</v>
+        <v>3314</v>
       </c>
       <c r="C4" t="n">
-        <v>4616</v>
+        <v>6073</v>
       </c>
       <c r="D4" t="n">
-        <v>8617</v>
+        <v>6637</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1778</v>
+        <v>2360</v>
       </c>
       <c r="C5" t="n">
-        <v>4430</v>
+        <v>5139</v>
       </c>
       <c r="D5" t="n">
-        <v>3929</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1142</v>
+        <v>1436</v>
       </c>
       <c r="C6" t="n">
-        <v>3984</v>
+        <v>3824</v>
       </c>
       <c r="D6" t="n">
-        <v>1603</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>575</v>
+        <v>731</v>
       </c>
       <c r="C7" t="n">
-        <v>2847</v>
+        <v>2430</v>
       </c>
       <c r="D7" t="n">
-        <v>774</v>
+        <v>694</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>232</v>
+        <v>306</v>
       </c>
       <c r="C8" t="n">
-        <v>1568</v>
+        <v>1182</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="C9" t="n">
-        <v>663</v>
+        <v>486</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8246</v>
+        <v>9910</v>
       </c>
       <c r="C2" t="n">
-        <v>8214</v>
+        <v>11380</v>
       </c>
       <c r="D2" t="n">
-        <v>25072</v>
+        <v>31915</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3390</v>
+        <v>5123</v>
       </c>
       <c r="C3" t="n">
-        <v>6645</v>
+        <v>7324</v>
       </c>
       <c r="D3" t="n">
-        <v>15815</v>
+        <v>13673</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2201</v>
+        <v>3318</v>
       </c>
       <c r="C4" t="n">
-        <v>4835</v>
+        <v>6008</v>
       </c>
       <c r="D4" t="n">
-        <v>9325</v>
+        <v>7214</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1777</v>
+        <v>2462</v>
       </c>
       <c r="C5" t="n">
-        <v>4372</v>
+        <v>5377</v>
       </c>
       <c r="D5" t="n">
-        <v>4484</v>
+        <v>3211</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1281</v>
+        <v>1638</v>
       </c>
       <c r="C6" t="n">
-        <v>4128</v>
+        <v>4332</v>
       </c>
       <c r="D6" t="n">
-        <v>1879</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>709</v>
+        <v>903</v>
       </c>
       <c r="C7" t="n">
-        <v>3263</v>
+        <v>2965</v>
       </c>
       <c r="D7" t="n">
-        <v>879</v>
+        <v>754</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>317</v>
+        <v>415</v>
       </c>
       <c r="C8" t="n">
-        <v>2040</v>
+        <v>1659</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C9" t="n">
-        <v>999</v>
+        <v>751</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>421</v>
+        <v>328</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7354</v>
+        <v>9073</v>
       </c>
       <c r="C2" t="n">
-        <v>5651</v>
+        <v>7738</v>
       </c>
       <c r="D2" t="n">
-        <v>20816</v>
+        <v>26188</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4012</v>
+        <v>6056</v>
       </c>
       <c r="C3" t="n">
-        <v>9295</v>
+        <v>10876</v>
       </c>
       <c r="D3" t="n">
-        <v>17287</v>
+        <v>14685</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1641</v>
+        <v>2274</v>
       </c>
       <c r="C4" t="n">
-        <v>6842</v>
+        <v>8449</v>
       </c>
       <c r="D4" t="n">
-        <v>9186</v>
+        <v>6928</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1183</v>
+        <v>1513</v>
       </c>
       <c r="C5" t="n">
-        <v>4045</v>
+        <v>4245</v>
       </c>
       <c r="D5" t="n">
-        <v>3046</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>655</v>
+        <v>834</v>
       </c>
       <c r="C6" t="n">
-        <v>3197</v>
+        <v>2905</v>
       </c>
       <c r="D6" t="n">
-        <v>861</v>
+        <v>738</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>383</v>
       </c>
       <c r="C7" t="n">
-        <v>1999</v>
+        <v>1625</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="C8" t="n">
-        <v>979</v>
+        <v>735</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>412</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4374</v>
+        <v>5461</v>
       </c>
       <c r="C2" t="n">
-        <v>3238</v>
+        <v>3745</v>
       </c>
       <c r="D2" t="n">
-        <v>14840</v>
+        <v>18063</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4609</v>
+        <v>6308</v>
       </c>
       <c r="C3" t="n">
-        <v>6945</v>
+        <v>8648</v>
       </c>
       <c r="D3" t="n">
-        <v>16937</v>
+        <v>15403</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2224</v>
+        <v>3207</v>
       </c>
       <c r="C4" t="n">
-        <v>8092</v>
+        <v>9634</v>
       </c>
       <c r="D4" t="n">
-        <v>10161</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1286</v>
+        <v>1700</v>
       </c>
       <c r="C5" t="n">
-        <v>5282</v>
+        <v>6095</v>
       </c>
       <c r="D5" t="n">
-        <v>3778</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>779</v>
+        <v>991</v>
       </c>
       <c r="C6" t="n">
-        <v>3646</v>
+        <v>3516</v>
       </c>
       <c r="D6" t="n">
-        <v>1085</v>
+        <v>895</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>361</v>
       </c>
       <c r="C7" t="n">
-        <v>2491</v>
+        <v>2118</v>
       </c>
       <c r="D7" t="n">
-        <v>529</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>1276</v>
+        <v>991</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>460</v>
+        <v>368</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4027</v>
+        <v>6832</v>
       </c>
       <c r="C2" t="n">
-        <v>6448</v>
+        <v>5326</v>
       </c>
       <c r="D2" t="n">
-        <v>15567</v>
+        <v>16611</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3786</v>
+        <v>5049</v>
       </c>
       <c r="C3" t="n">
-        <v>4588</v>
+        <v>5625</v>
       </c>
       <c r="D3" t="n">
-        <v>15513</v>
+        <v>14729</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2784</v>
+        <v>3870</v>
       </c>
       <c r="C4" t="n">
-        <v>7439</v>
+        <v>8950</v>
       </c>
       <c r="D4" t="n">
-        <v>10957</v>
+        <v>8998</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1492</v>
+        <v>2070</v>
       </c>
       <c r="C5" t="n">
-        <v>6466</v>
+        <v>7691</v>
       </c>
       <c r="D5" t="n">
-        <v>4643</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>905</v>
+        <v>1188</v>
       </c>
       <c r="C6" t="n">
-        <v>4333</v>
+        <v>4621</v>
       </c>
       <c r="D6" t="n">
-        <v>1458</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>411</v>
+        <v>529</v>
       </c>
       <c r="C7" t="n">
-        <v>3012</v>
+        <v>2740</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="C8" t="n">
-        <v>1776</v>
+        <v>1453</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>768</v>
+        <v>603</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>312</v>
+        <v>273</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2379</v>
+        <v>4044</v>
       </c>
       <c r="C2" t="n">
-        <v>3018</v>
+        <v>2502</v>
       </c>
       <c r="D2" t="n">
-        <v>10866</v>
+        <v>11575</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3740</v>
+        <v>5327</v>
       </c>
       <c r="C3" t="n">
-        <v>5073</v>
+        <v>5353</v>
       </c>
       <c r="D3" t="n">
-        <v>15171</v>
+        <v>14594</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3067</v>
+        <v>4239</v>
       </c>
       <c r="C4" t="n">
-        <v>7067</v>
+        <v>8537</v>
       </c>
       <c r="D4" t="n">
-        <v>11588</v>
+        <v>9685</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1571</v>
+        <v>2144</v>
       </c>
       <c r="C5" t="n">
-        <v>7722</v>
+        <v>9176</v>
       </c>
       <c r="D5" t="n">
-        <v>4885</v>
+        <v>3729</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>747</v>
+        <v>971</v>
       </c>
       <c r="C6" t="n">
-        <v>5276</v>
+        <v>5512</v>
       </c>
       <c r="D6" t="n">
-        <v>1418</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="C7" t="n">
-        <v>3178</v>
+        <v>2781</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1292</v>
+        <v>1032</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2553</v>
+        <v>4287</v>
       </c>
       <c r="C2" t="n">
-        <v>7921</v>
+        <v>6470</v>
       </c>
       <c r="D2" t="n">
-        <v>10213</v>
+        <v>18607</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2724</v>
+        <v>4094</v>
       </c>
       <c r="C3" t="n">
-        <v>3690</v>
+        <v>3621</v>
       </c>
       <c r="D3" t="n">
-        <v>13711</v>
+        <v>13342</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2915</v>
+        <v>4117</v>
       </c>
       <c r="C4" t="n">
-        <v>5982</v>
+        <v>6943</v>
       </c>
       <c r="D4" t="n">
-        <v>11786</v>
+        <v>10144</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1927</v>
+        <v>2630</v>
       </c>
       <c r="C5" t="n">
-        <v>7339</v>
+        <v>8702</v>
       </c>
       <c r="D5" t="n">
-        <v>5701</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>968</v>
+        <v>1269</v>
       </c>
       <c r="C6" t="n">
-        <v>6364</v>
+        <v>7116</v>
       </c>
       <c r="D6" t="n">
-        <v>1865</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>365</v>
       </c>
       <c r="C7" t="n">
-        <v>4030</v>
+        <v>3877</v>
       </c>
       <c r="D7" t="n">
-        <v>697</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>2000</v>
+        <v>1686</v>
       </c>
       <c r="D8" t="n">
         <v>397</v>
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>633</v>
+        <v>522</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
         <v>133</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1790</v>
+        <v>3096</v>
       </c>
       <c r="C2" t="n">
-        <v>4909</v>
+        <v>4722</v>
       </c>
       <c r="D2" t="n">
-        <v>8360</v>
+        <v>14353</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2339</v>
+        <v>3642</v>
       </c>
       <c r="C3" t="n">
-        <v>4906</v>
+        <v>4293</v>
       </c>
       <c r="D3" t="n">
-        <v>12545</v>
+        <v>13376</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2633</v>
+        <v>3782</v>
       </c>
       <c r="C4" t="n">
-        <v>5105</v>
+        <v>5659</v>
       </c>
       <c r="D4" t="n">
-        <v>11912</v>
+        <v>10332</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2095</v>
+        <v>2910</v>
       </c>
       <c r="C5" t="n">
-        <v>6915</v>
+        <v>8230</v>
       </c>
       <c r="D5" t="n">
-        <v>6224</v>
+        <v>4978</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1146</v>
+        <v>1491</v>
       </c>
       <c r="C6" t="n">
-        <v>6932</v>
+        <v>7889</v>
       </c>
       <c r="D6" t="n">
-        <v>2228</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>251</v>
+        <v>328</v>
       </c>
       <c r="C7" t="n">
-        <v>4876</v>
+        <v>4903</v>
       </c>
       <c r="D7" t="n">
-        <v>779</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>2524</v>
+        <v>2181</v>
       </c>
       <c r="D8" t="n">
         <v>409</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>735</v>
+        <v>597</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2651</v>
+        <v>4915</v>
       </c>
       <c r="C2" t="n">
-        <v>7582</v>
+        <v>16191</v>
       </c>
       <c r="D2" t="n">
-        <v>11269</v>
+        <v>17533</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1805</v>
+        <v>2908</v>
       </c>
       <c r="C3" t="n">
-        <v>4404</v>
+        <v>4011</v>
       </c>
       <c r="D3" t="n">
-        <v>11239</v>
+        <v>12637</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2198</v>
+        <v>3244</v>
       </c>
       <c r="C4" t="n">
-        <v>4914</v>
+        <v>4923</v>
       </c>
       <c r="D4" t="n">
-        <v>11641</v>
+        <v>10456</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2098</v>
+        <v>2918</v>
       </c>
       <c r="C5" t="n">
-        <v>6041</v>
+        <v>7022</v>
       </c>
       <c r="D5" t="n">
-        <v>6799</v>
+        <v>5546</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1362</v>
+        <v>1825</v>
       </c>
       <c r="C6" t="n">
-        <v>6867</v>
+        <v>7953</v>
       </c>
       <c r="D6" t="n">
-        <v>2698</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>470</v>
+        <v>613</v>
       </c>
       <c r="C7" t="n">
-        <v>5639</v>
+        <v>6061</v>
       </c>
       <c r="D7" t="n">
-        <v>933</v>
+        <v>823</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>3377</v>
+        <v>3113</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1320</v>
+        <v>1114</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>377</v>
+        <v>332</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
         <v>138</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
         <v>37</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5062</v>
+        <v>6969</v>
       </c>
       <c r="C2" t="n">
-        <v>9395</v>
+        <v>3325</v>
       </c>
       <c r="D2" t="n">
-        <v>19970</v>
+        <v>8843</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1897</v>
+        <v>3556</v>
       </c>
       <c r="C2" t="n">
-        <v>4306</v>
+        <v>9326</v>
       </c>
       <c r="D2" t="n">
-        <v>8293</v>
+        <v>13044</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2482</v>
+        <v>3921</v>
       </c>
       <c r="C3" t="n">
-        <v>5521</v>
+        <v>7092</v>
       </c>
       <c r="D3" t="n">
-        <v>12292</v>
+        <v>13816</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3041</v>
+        <v>4355</v>
       </c>
       <c r="C4" t="n">
-        <v>7038</v>
+        <v>7335</v>
       </c>
       <c r="D4" t="n">
-        <v>12024</v>
+        <v>10666</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1316</v>
+        <v>1740</v>
       </c>
       <c r="C5" t="n">
-        <v>9327</v>
+        <v>10829</v>
       </c>
       <c r="D5" t="n">
-        <v>6217</v>
+        <v>5042</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>434</v>
+        <v>566</v>
       </c>
       <c r="C6" t="n">
-        <v>6872</v>
+        <v>7420</v>
       </c>
       <c r="D6" t="n">
-        <v>2117</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>3309</v>
+        <v>3050</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1293</v>
+        <v>1091</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>369</v>
+        <v>325</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
         <v>135</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
         <v>36</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5948</v>
+        <v>7349</v>
       </c>
       <c r="C2" t="n">
-        <v>7219</v>
+        <v>7795</v>
       </c>
       <c r="D2" t="n">
-        <v>21880</v>
+        <v>12378</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2151</v>
+        <v>2960</v>
       </c>
       <c r="C3" t="n">
-        <v>4735</v>
+        <v>1675</v>
       </c>
       <c r="D3" t="n">
-        <v>3994</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4588</v>
+        <v>4863</v>
       </c>
       <c r="C2" t="n">
-        <v>10568</v>
+        <v>7053</v>
       </c>
       <c r="D2" t="n">
-        <v>28857</v>
+        <v>13522</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3324</v>
+        <v>4234</v>
       </c>
       <c r="C3" t="n">
-        <v>5295</v>
+        <v>4477</v>
       </c>
       <c r="D3" t="n">
-        <v>6704</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>968</v>
+        <v>1319</v>
       </c>
       <c r="C4" t="n">
-        <v>2818</v>
+        <v>1040</v>
       </c>
       <c r="D4" t="n">
-        <v>1986</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5793</v>
+        <v>5427</v>
       </c>
       <c r="C2" t="n">
-        <v>6699</v>
+        <v>8866</v>
       </c>
       <c r="D2" t="n">
-        <v>28919</v>
+        <v>20698</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3234</v>
+        <v>3746</v>
       </c>
       <c r="C3" t="n">
-        <v>7038</v>
+        <v>5091</v>
       </c>
       <c r="D3" t="n">
-        <v>9765</v>
+        <v>4997</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1796</v>
+        <v>2351</v>
       </c>
       <c r="C4" t="n">
-        <v>4138</v>
+        <v>2965</v>
       </c>
       <c r="D4" t="n">
-        <v>2831</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>451</v>
+        <v>601</v>
       </c>
       <c r="C5" t="n">
-        <v>1612</v>
+        <v>662</v>
       </c>
       <c r="D5" t="n">
-        <v>1305</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5502</v>
+        <v>7276</v>
       </c>
       <c r="C2" t="n">
-        <v>5893</v>
+        <v>6417</v>
       </c>
       <c r="D2" t="n">
-        <v>24149</v>
+        <v>20769</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3619</v>
+        <v>3732</v>
       </c>
       <c r="C3" t="n">
-        <v>5987</v>
+        <v>6122</v>
       </c>
       <c r="D3" t="n">
-        <v>11988</v>
+        <v>7031</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2124</v>
+        <v>2581</v>
       </c>
       <c r="C4" t="n">
-        <v>5583</v>
+        <v>4017</v>
       </c>
       <c r="D4" t="n">
-        <v>4009</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>910</v>
+        <v>1232</v>
       </c>
       <c r="C5" t="n">
-        <v>2848</v>
+        <v>1864</v>
       </c>
       <c r="D5" t="n">
-        <v>1516</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>259</v>
+        <v>321</v>
       </c>
       <c r="C6" t="n">
-        <v>954</v>
+        <v>482</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5453</v>
+        <v>8092</v>
       </c>
       <c r="C2" t="n">
-        <v>7168</v>
+        <v>9154</v>
       </c>
       <c r="D2" t="n">
-        <v>20273</v>
+        <v>17649</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3278</v>
+        <v>4008</v>
       </c>
       <c r="C3" t="n">
-        <v>4869</v>
+        <v>5138</v>
       </c>
       <c r="D3" t="n">
-        <v>12224</v>
+        <v>8113</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1755</v>
+        <v>1947</v>
       </c>
       <c r="C4" t="n">
-        <v>4746</v>
+        <v>4211</v>
       </c>
       <c r="D4" t="n">
-        <v>4661</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>786</v>
+        <v>997</v>
       </c>
       <c r="C5" t="n">
-        <v>3076</v>
+        <v>2197</v>
       </c>
       <c r="D5" t="n">
-        <v>1539</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>271</v>
+        <v>370</v>
       </c>
       <c r="C6" t="n">
-        <v>1272</v>
+        <v>790</v>
       </c>
       <c r="D6" t="n">
-        <v>788</v>
+        <v>770</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>408</v>
+        <v>266</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
         <v>63</v>
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4364</v>
+        <v>6484</v>
       </c>
       <c r="C2" t="n">
-        <v>5228</v>
+        <v>7925</v>
       </c>
       <c r="D2" t="n">
-        <v>23052</v>
+        <v>26813</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3609</v>
+        <v>5035</v>
       </c>
       <c r="C3" t="n">
-        <v>5331</v>
+        <v>6462</v>
       </c>
       <c r="D3" t="n">
-        <v>12676</v>
+        <v>9181</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2199</v>
+        <v>2606</v>
       </c>
       <c r="C4" t="n">
-        <v>4720</v>
+        <v>4692</v>
       </c>
       <c r="D4" t="n">
-        <v>6044</v>
+        <v>3814</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1125</v>
+        <v>1323</v>
       </c>
       <c r="C5" t="n">
-        <v>3973</v>
+        <v>3350</v>
       </c>
       <c r="D5" t="n">
-        <v>2076</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>481</v>
+        <v>638</v>
       </c>
       <c r="C6" t="n">
-        <v>2248</v>
+        <v>1590</v>
       </c>
       <c r="D6" t="n">
-        <v>921</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="C7" t="n">
-        <v>890</v>
+        <v>563</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>322</v>
+        <v>246</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4287</v>
+        <v>6037</v>
       </c>
       <c r="C2" t="n">
-        <v>6387</v>
+        <v>9093</v>
       </c>
       <c r="D2" t="n">
-        <v>26587</v>
+        <v>21334</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3274</v>
+        <v>4729</v>
       </c>
       <c r="C3" t="n">
-        <v>4575</v>
+        <v>6284</v>
       </c>
       <c r="D3" t="n">
-        <v>13545</v>
+        <v>11341</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2487</v>
+        <v>3256</v>
       </c>
       <c r="C4" t="n">
-        <v>4962</v>
+        <v>5551</v>
       </c>
       <c r="D4" t="n">
-        <v>7011</v>
+        <v>4728</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1433</v>
+        <v>1725</v>
       </c>
       <c r="C5" t="n">
-        <v>4291</v>
+        <v>4027</v>
       </c>
       <c r="D5" t="n">
-        <v>2736</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>721</v>
+        <v>886</v>
       </c>
       <c r="C6" t="n">
-        <v>3117</v>
+        <v>2517</v>
       </c>
       <c r="D6" t="n">
-        <v>1098</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>277</v>
+        <v>377</v>
       </c>
       <c r="C7" t="n">
-        <v>1572</v>
+        <v>1106</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>605</v>
+        <v>407</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_22_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_22_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7688</v>
+        <v>1331</v>
       </c>
       <c r="C2" t="n">
-        <v>7823</v>
+        <v>2012</v>
       </c>
       <c r="D2" t="n">
-        <v>21162</v>
+        <v>17716</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4397</v>
+        <v>2295</v>
       </c>
       <c r="C3" t="n">
-        <v>6715</v>
+        <v>5404</v>
       </c>
       <c r="D3" t="n">
-        <v>12061</v>
+        <v>18035</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3406</v>
+        <v>1433</v>
       </c>
       <c r="C4" t="n">
-        <v>5822</v>
+        <v>6419</v>
       </c>
       <c r="D4" t="n">
-        <v>5790</v>
+        <v>7529</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2129</v>
+        <v>693</v>
       </c>
       <c r="C5" t="n">
-        <v>4718</v>
+        <v>3606</v>
       </c>
       <c r="D5" t="n">
-        <v>2286</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1168</v>
+        <v>299</v>
       </c>
       <c r="C6" t="n">
-        <v>3204</v>
+        <v>1396</v>
       </c>
       <c r="D6" t="n">
-        <v>1063</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>544</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
-        <v>1796</v>
+        <v>585</v>
       </c>
       <c r="D7" t="n">
-        <v>646</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>209</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>731</v>
+        <v>344</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8590</v>
+        <v>1517</v>
       </c>
       <c r="C2" t="n">
-        <v>11030</v>
+        <v>7482</v>
       </c>
       <c r="D2" t="n">
-        <v>29025</v>
+        <v>21769</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4755</v>
+        <v>1547</v>
       </c>
       <c r="C3" t="n">
-        <v>6352</v>
+        <v>3112</v>
       </c>
       <c r="D3" t="n">
-        <v>12488</v>
+        <v>16858</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3314</v>
+        <v>1602</v>
       </c>
       <c r="C4" t="n">
-        <v>6073</v>
+        <v>5781</v>
       </c>
       <c r="D4" t="n">
-        <v>6637</v>
+        <v>9216</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2360</v>
+        <v>914</v>
       </c>
       <c r="C5" t="n">
-        <v>5139</v>
+        <v>5050</v>
       </c>
       <c r="D5" t="n">
-        <v>2732</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1436</v>
+        <v>436</v>
       </c>
       <c r="C6" t="n">
-        <v>3824</v>
+        <v>2484</v>
       </c>
       <c r="D6" t="n">
-        <v>1236</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>731</v>
+        <v>165</v>
       </c>
       <c r="C7" t="n">
-        <v>2430</v>
+        <v>987</v>
       </c>
       <c r="D7" t="n">
-        <v>694</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1182</v>
+        <v>461</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>486</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9910</v>
+        <v>794</v>
       </c>
       <c r="C2" t="n">
-        <v>11380</v>
+        <v>3016</v>
       </c>
       <c r="D2" t="n">
-        <v>31915</v>
+        <v>14643</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5123</v>
+        <v>1479</v>
       </c>
       <c r="C3" t="n">
-        <v>7324</v>
+        <v>4725</v>
       </c>
       <c r="D3" t="n">
-        <v>13673</v>
+        <v>17028</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3318</v>
+        <v>1755</v>
       </c>
       <c r="C4" t="n">
-        <v>6008</v>
+        <v>5195</v>
       </c>
       <c r="D4" t="n">
-        <v>7214</v>
+        <v>10258</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2462</v>
+        <v>923</v>
       </c>
       <c r="C5" t="n">
-        <v>5377</v>
+        <v>5875</v>
       </c>
       <c r="D5" t="n">
-        <v>3211</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1638</v>
+        <v>348</v>
       </c>
       <c r="C6" t="n">
-        <v>4332</v>
+        <v>3267</v>
       </c>
       <c r="D6" t="n">
-        <v>1408</v>
+        <v>987</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>903</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>2965</v>
+        <v>1000</v>
       </c>
       <c r="D7" t="n">
-        <v>754</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>415</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1659</v>
+        <v>473</v>
       </c>
       <c r="D8" t="n">
-        <v>487</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>161</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>751</v>
+        <v>242</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>328</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9073</v>
+        <v>617</v>
       </c>
       <c r="C2" t="n">
-        <v>7738</v>
+        <v>5251</v>
       </c>
       <c r="D2" t="n">
-        <v>26188</v>
+        <v>20358</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6056</v>
+        <v>991</v>
       </c>
       <c r="C3" t="n">
-        <v>10876</v>
+        <v>3371</v>
       </c>
       <c r="D3" t="n">
-        <v>14685</v>
+        <v>15466</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2274</v>
+        <v>1449</v>
       </c>
       <c r="C4" t="n">
-        <v>8449</v>
+        <v>4884</v>
       </c>
       <c r="D4" t="n">
-        <v>6928</v>
+        <v>11279</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1513</v>
+        <v>1150</v>
       </c>
       <c r="C5" t="n">
-        <v>4245</v>
+        <v>5463</v>
       </c>
       <c r="D5" t="n">
-        <v>2242</v>
+        <v>4536</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>834</v>
+        <v>534</v>
       </c>
       <c r="C6" t="n">
-        <v>2905</v>
+        <v>4548</v>
       </c>
       <c r="D6" t="n">
-        <v>738</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>383</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
-        <v>1625</v>
+        <v>2041</v>
       </c>
       <c r="D7" t="n">
-        <v>477</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>735</v>
+        <v>698</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5461</v>
+        <v>331</v>
       </c>
       <c r="C2" t="n">
-        <v>3745</v>
+        <v>3164</v>
       </c>
       <c r="D2" t="n">
-        <v>18063</v>
+        <v>14420</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6308</v>
+        <v>742</v>
       </c>
       <c r="C3" t="n">
-        <v>8648</v>
+        <v>3834</v>
       </c>
       <c r="D3" t="n">
-        <v>15403</v>
+        <v>15240</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3207</v>
+        <v>1192</v>
       </c>
       <c r="C4" t="n">
-        <v>9634</v>
+        <v>4211</v>
       </c>
       <c r="D4" t="n">
-        <v>8041</v>
+        <v>11687</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1700</v>
+        <v>1217</v>
       </c>
       <c r="C5" t="n">
-        <v>6095</v>
+        <v>5314</v>
       </c>
       <c r="D5" t="n">
-        <v>2801</v>
+        <v>5391</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>991</v>
+        <v>664</v>
       </c>
       <c r="C6" t="n">
-        <v>3516</v>
+        <v>5068</v>
       </c>
       <c r="D6" t="n">
-        <v>895</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>361</v>
+        <v>173</v>
       </c>
       <c r="C7" t="n">
-        <v>2118</v>
+        <v>2941</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>991</v>
+        <v>1055</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>368</v>
+        <v>433</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6832</v>
+        <v>558</v>
       </c>
       <c r="C2" t="n">
-        <v>5326</v>
+        <v>13560</v>
       </c>
       <c r="D2" t="n">
-        <v>16611</v>
+        <v>17714</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5049</v>
+        <v>480</v>
       </c>
       <c r="C3" t="n">
-        <v>5625</v>
+        <v>3119</v>
       </c>
       <c r="D3" t="n">
-        <v>14729</v>
+        <v>14219</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3870</v>
+        <v>885</v>
       </c>
       <c r="C4" t="n">
-        <v>8950</v>
+        <v>3938</v>
       </c>
       <c r="D4" t="n">
-        <v>8998</v>
+        <v>11911</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2070</v>
+        <v>1115</v>
       </c>
       <c r="C5" t="n">
-        <v>7691</v>
+        <v>4684</v>
       </c>
       <c r="D5" t="n">
-        <v>3520</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1188</v>
+        <v>815</v>
       </c>
       <c r="C6" t="n">
-        <v>4621</v>
+        <v>5178</v>
       </c>
       <c r="D6" t="n">
-        <v>1157</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>529</v>
+        <v>314</v>
       </c>
       <c r="C7" t="n">
-        <v>2740</v>
+        <v>3856</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>847</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>1453</v>
+        <v>1841</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>505</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>603</v>
+        <v>674</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4044</v>
+        <v>370</v>
       </c>
       <c r="C2" t="n">
-        <v>2502</v>
+        <v>6942</v>
       </c>
       <c r="D2" t="n">
-        <v>11575</v>
+        <v>12755</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5327</v>
+        <v>726</v>
       </c>
       <c r="C3" t="n">
-        <v>5353</v>
+        <v>6360</v>
       </c>
       <c r="D3" t="n">
-        <v>14594</v>
+        <v>15502</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4239</v>
+        <v>1460</v>
       </c>
       <c r="C4" t="n">
-        <v>8537</v>
+        <v>5488</v>
       </c>
       <c r="D4" t="n">
-        <v>9685</v>
+        <v>12307</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2144</v>
+        <v>835</v>
       </c>
       <c r="C5" t="n">
-        <v>9176</v>
+        <v>7082</v>
       </c>
       <c r="D5" t="n">
-        <v>3729</v>
+        <v>5673</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>971</v>
+        <v>290</v>
       </c>
       <c r="C6" t="n">
-        <v>5512</v>
+        <v>5098</v>
       </c>
       <c r="D6" t="n">
-        <v>1147</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>2781</v>
+        <v>1804</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1032</v>
+        <v>660</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4287</v>
+        <v>189</v>
       </c>
       <c r="C2" t="n">
-        <v>6470</v>
+        <v>3589</v>
       </c>
       <c r="D2" t="n">
-        <v>18607</v>
+        <v>9573</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4094</v>
+        <v>487</v>
       </c>
       <c r="C3" t="n">
-        <v>3621</v>
+        <v>5852</v>
       </c>
       <c r="D3" t="n">
-        <v>13342</v>
+        <v>13995</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4117</v>
+        <v>944</v>
       </c>
       <c r="C4" t="n">
-        <v>6943</v>
+        <v>5632</v>
       </c>
       <c r="D4" t="n">
-        <v>10144</v>
+        <v>11968</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2630</v>
+        <v>785</v>
       </c>
       <c r="C5" t="n">
-        <v>8702</v>
+        <v>5561</v>
       </c>
       <c r="D5" t="n">
-        <v>4473</v>
+        <v>5972</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1269</v>
+        <v>293</v>
       </c>
       <c r="C6" t="n">
-        <v>7116</v>
+        <v>4940</v>
       </c>
       <c r="D6" t="n">
-        <v>1479</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>365</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>3877</v>
+        <v>2320</v>
       </c>
       <c r="D7" t="n">
-        <v>641</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1686</v>
+        <v>726</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>522</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>131</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3096</v>
+        <v>368</v>
       </c>
       <c r="C2" t="n">
-        <v>4722</v>
+        <v>5573</v>
       </c>
       <c r="D2" t="n">
-        <v>14353</v>
+        <v>12103</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3642</v>
+        <v>288</v>
       </c>
       <c r="C3" t="n">
-        <v>4293</v>
+        <v>4053</v>
       </c>
       <c r="D3" t="n">
-        <v>13376</v>
+        <v>12279</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3782</v>
+        <v>641</v>
       </c>
       <c r="C4" t="n">
-        <v>5659</v>
+        <v>5637</v>
       </c>
       <c r="D4" t="n">
-        <v>10332</v>
+        <v>11993</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2910</v>
+        <v>782</v>
       </c>
       <c r="C5" t="n">
-        <v>8230</v>
+        <v>5536</v>
       </c>
       <c r="D5" t="n">
-        <v>4978</v>
+        <v>6884</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1491</v>
+        <v>469</v>
       </c>
       <c r="C6" t="n">
-        <v>7889</v>
+        <v>5201</v>
       </c>
       <c r="D6" t="n">
-        <v>1763</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>328</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>4903</v>
+        <v>3651</v>
       </c>
       <c r="D7" t="n">
-        <v>706</v>
+        <v>830</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>2181</v>
+        <v>1482</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>597</v>
+        <v>475</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4915</v>
+        <v>291</v>
       </c>
       <c r="C2" t="n">
-        <v>16191</v>
+        <v>14932</v>
       </c>
       <c r="D2" t="n">
-        <v>17533</v>
+        <v>13643</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2908</v>
+        <v>266</v>
       </c>
       <c r="C3" t="n">
-        <v>4011</v>
+        <v>4191</v>
       </c>
       <c r="D3" t="n">
-        <v>12637</v>
+        <v>11408</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3244</v>
+        <v>424</v>
       </c>
       <c r="C4" t="n">
-        <v>4923</v>
+        <v>4713</v>
       </c>
       <c r="D4" t="n">
-        <v>10456</v>
+        <v>11677</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2918</v>
+        <v>655</v>
       </c>
       <c r="C5" t="n">
-        <v>7022</v>
+        <v>5417</v>
       </c>
       <c r="D5" t="n">
-        <v>5546</v>
+        <v>7442</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1825</v>
+        <v>560</v>
       </c>
       <c r="C6" t="n">
-        <v>7953</v>
+        <v>5307</v>
       </c>
       <c r="D6" t="n">
-        <v>2141</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>613</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>6061</v>
+        <v>4378</v>
       </c>
       <c r="D7" t="n">
-        <v>823</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>3113</v>
+        <v>2459</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1114</v>
+        <v>909</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6969</v>
+        <v>4649</v>
       </c>
       <c r="C2" t="n">
-        <v>3325</v>
+        <v>7227</v>
       </c>
       <c r="D2" t="n">
-        <v>8843</v>
+        <v>8366</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3556</v>
+        <v>974</v>
       </c>
       <c r="C2" t="n">
-        <v>9326</v>
+        <v>25303</v>
       </c>
       <c r="D2" t="n">
-        <v>13044</v>
+        <v>20240</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3921</v>
+        <v>229</v>
       </c>
       <c r="C3" t="n">
-        <v>7092</v>
+        <v>7826</v>
       </c>
       <c r="D3" t="n">
-        <v>13816</v>
+        <v>10945</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4355</v>
+        <v>311</v>
       </c>
       <c r="C4" t="n">
-        <v>7335</v>
+        <v>4329</v>
       </c>
       <c r="D4" t="n">
-        <v>10666</v>
+        <v>11168</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1740</v>
+        <v>522</v>
       </c>
       <c r="C5" t="n">
-        <v>10829</v>
+        <v>4986</v>
       </c>
       <c r="D5" t="n">
-        <v>5042</v>
+        <v>7866</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="C6" t="n">
-        <v>7420</v>
+        <v>5304</v>
       </c>
       <c r="D6" t="n">
-        <v>1750</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>340</v>
       </c>
       <c r="C7" t="n">
-        <v>3050</v>
+        <v>4724</v>
       </c>
       <c r="D7" t="n">
-        <v>532</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>1091</v>
+        <v>3247</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>325</v>
+        <v>1516</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>528</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>196</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>62</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7349</v>
+        <v>4978</v>
       </c>
       <c r="C2" t="n">
-        <v>7795</v>
+        <v>5201</v>
       </c>
       <c r="D2" t="n">
-        <v>12378</v>
+        <v>24214</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2960</v>
+        <v>1536</v>
       </c>
       <c r="C3" t="n">
-        <v>1675</v>
+        <v>2854</v>
       </c>
       <c r="D3" t="n">
-        <v>2124</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4863</v>
+        <v>2337</v>
       </c>
       <c r="C2" t="n">
-        <v>7053</v>
+        <v>5463</v>
       </c>
       <c r="D2" t="n">
-        <v>13522</v>
+        <v>29400</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4234</v>
+        <v>2752</v>
       </c>
       <c r="C3" t="n">
-        <v>4477</v>
+        <v>3663</v>
       </c>
       <c r="D3" t="n">
-        <v>3690</v>
+        <v>5581</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1319</v>
+        <v>736</v>
       </c>
       <c r="C4" t="n">
-        <v>1040</v>
+        <v>1828</v>
       </c>
       <c r="D4" t="n">
-        <v>1609</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5427</v>
+        <v>1946</v>
       </c>
       <c r="C2" t="n">
-        <v>8866</v>
+        <v>4633</v>
       </c>
       <c r="D2" t="n">
-        <v>20698</v>
+        <v>26025</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3746</v>
+        <v>2097</v>
       </c>
       <c r="C3" t="n">
-        <v>5091</v>
+        <v>4045</v>
       </c>
       <c r="D3" t="n">
-        <v>4997</v>
+        <v>9171</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2351</v>
+        <v>1532</v>
       </c>
       <c r="C4" t="n">
-        <v>2965</v>
+        <v>2882</v>
       </c>
       <c r="D4" t="n">
-        <v>1959</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>601</v>
+        <v>361</v>
       </c>
       <c r="C5" t="n">
-        <v>662</v>
+        <v>1135</v>
       </c>
       <c r="D5" t="n">
-        <v>1215</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7276</v>
+        <v>1956</v>
       </c>
       <c r="C2" t="n">
-        <v>6417</v>
+        <v>5552</v>
       </c>
       <c r="D2" t="n">
-        <v>20769</v>
+        <v>38836</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3732</v>
+        <v>1671</v>
       </c>
       <c r="C3" t="n">
-        <v>6122</v>
+        <v>3777</v>
       </c>
       <c r="D3" t="n">
-        <v>7031</v>
+        <v>11207</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2581</v>
+        <v>1572</v>
       </c>
       <c r="C4" t="n">
-        <v>4017</v>
+        <v>3491</v>
       </c>
       <c r="D4" t="n">
-        <v>2434</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1232</v>
+        <v>806</v>
       </c>
       <c r="C5" t="n">
-        <v>1864</v>
+        <v>2084</v>
       </c>
       <c r="D5" t="n">
-        <v>1313</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>321</v>
+        <v>209</v>
       </c>
       <c r="C6" t="n">
-        <v>482</v>
+        <v>727</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8092</v>
+        <v>3828</v>
       </c>
       <c r="C2" t="n">
-        <v>9154</v>
+        <v>6649</v>
       </c>
       <c r="D2" t="n">
-        <v>17649</v>
+        <v>32310</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4008</v>
+        <v>1490</v>
       </c>
       <c r="C3" t="n">
-        <v>5138</v>
+        <v>4090</v>
       </c>
       <c r="D3" t="n">
-        <v>8113</v>
+        <v>14617</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1947</v>
+        <v>1392</v>
       </c>
       <c r="C4" t="n">
-        <v>4211</v>
+        <v>3574</v>
       </c>
       <c r="D4" t="n">
-        <v>2770</v>
+        <v>4757</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>997</v>
+        <v>1033</v>
       </c>
       <c r="C5" t="n">
-        <v>2197</v>
+        <v>2783</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>370</v>
+        <v>439</v>
       </c>
       <c r="C6" t="n">
-        <v>790</v>
+        <v>1409</v>
       </c>
       <c r="D6" t="n">
-        <v>770</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>266</v>
+        <v>510</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6484</v>
+        <v>3040</v>
       </c>
       <c r="C2" t="n">
-        <v>7925</v>
+        <v>7984</v>
       </c>
       <c r="D2" t="n">
-        <v>26813</v>
+        <v>32717</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5035</v>
+        <v>2088</v>
       </c>
       <c r="C3" t="n">
-        <v>6462</v>
+        <v>4664</v>
       </c>
       <c r="D3" t="n">
-        <v>9181</v>
+        <v>16159</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2606</v>
+        <v>1234</v>
       </c>
       <c r="C4" t="n">
-        <v>4692</v>
+        <v>3727</v>
       </c>
       <c r="D4" t="n">
-        <v>3814</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1323</v>
+        <v>1073</v>
       </c>
       <c r="C5" t="n">
-        <v>3350</v>
+        <v>3119</v>
       </c>
       <c r="D5" t="n">
-        <v>1478</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C6" t="n">
-        <v>1590</v>
+        <v>2053</v>
       </c>
       <c r="D6" t="n">
-        <v>833</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="C7" t="n">
-        <v>563</v>
+        <v>927</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>246</v>
+        <v>397</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6037</v>
+        <v>2752</v>
       </c>
       <c r="C2" t="n">
-        <v>9093</v>
+        <v>4854</v>
       </c>
       <c r="D2" t="n">
-        <v>21334</v>
+        <v>25698</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4729</v>
+        <v>2510</v>
       </c>
       <c r="C3" t="n">
-        <v>6284</v>
+        <v>7226</v>
       </c>
       <c r="D3" t="n">
-        <v>11341</v>
+        <v>17733</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3256</v>
+        <v>991</v>
       </c>
       <c r="C4" t="n">
-        <v>5551</v>
+        <v>5355</v>
       </c>
       <c r="D4" t="n">
-        <v>4728</v>
+        <v>5681</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1725</v>
+        <v>585</v>
       </c>
       <c r="C5" t="n">
-        <v>4027</v>
+        <v>2011</v>
       </c>
       <c r="D5" t="n">
-        <v>1844</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>886</v>
+        <v>222</v>
       </c>
       <c r="C6" t="n">
-        <v>2517</v>
+        <v>908</v>
       </c>
       <c r="D6" t="n">
-        <v>938</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>1106</v>
+        <v>389</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>407</v>
+        <v>280</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
